--- a/reports/jobs_2026-09-16.xlsx
+++ b/reports/jobs_2026-09-16.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Applications Engineer</t>
+          <t>Information Developer (Technical Author)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/applications-engineer/33099/97112476448</t>
+          <t>https://careers.arm.com/job/cambridge/information-developer-technical-author/33099/97145326192</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>RTL Design Engineer – Memory Controller</t>
+          <t>Verification Engineer - AI/ML</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/rtl-design-engineer-memory-controller/33099/100674776368</t>
+          <t>https://careers.arm.com/job/lund/verification-engineer-ai-ml/33099/94291583344</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -606,17 +606,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>IOS Developer</t>
+          <t>Product Design Intern- Paytm</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -624,7 +624,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -632,12 +636,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/IOS-Developer_SR-42000</t>
+          <t>https://jobs.lever.co/paytm/3876b70d-85d2-4128-b3b1-91f078c10eb0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -647,198 +651,198 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Engineering Leader, Google COE</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Agnikul Cosmos</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>https://fractal.ai/careers/</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>mailto:%20humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://agnikul.in/careers</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Paytm</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Intern - TA Tech</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/paytm</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Agoda India</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Chiang Mai 1 available jobs</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Paytm</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Visual Design Intern- Paytm</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/paytm/4f0b8508-1fae-45ae-bc09-67291ea3c447</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/paytm</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Agoda India</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Dubai 0 available jobs</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/location/dubai/</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Zeta</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore - EC</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/zeta/72ee1884-8e8b-447b-ab96-aa76605b5f4a</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/zeta</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Agoda India</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/location/mumbai/</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -851,7 +855,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -859,12 +867,12 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -881,7 +889,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -894,11 +902,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -906,7 +910,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -928,7 +932,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -943,7 +947,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs Ok</t>
+          <t>Mumbai jobs Yokohama jobs</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -975,12 +979,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -988,11 +992,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 1 available jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1035,11 +1035,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1047,7 +1043,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1069,7 +1065,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1090,7 +1086,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1107,12 +1103,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1127,7 +1123,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs Yokohama jobs</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1137,12 +1133,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1154,17 +1150,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1180,12 +1176,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1197,17 +1193,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1223,12 +1219,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1240,12 +1236,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t xml:space="preserve">IT B2B/EDI Developer </t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1258,7 +1254,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000148716589</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1348,7 +1348,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1356,12 +1360,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1373,17 +1377,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1391,7 +1395,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1399,12 +1407,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1416,12 +1424,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Continental India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT B2B/EDI Developer </t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1436,7 +1444,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru/Gurugram Full-time</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1446,12 +1454,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000148716589</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/continental</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1463,17 +1471,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1483,7 +1491,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1493,12 +1501,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1515,12 +1523,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1528,11 +1536,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1540,7 +1544,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1562,12 +1566,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1577,7 +1581,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1587,7 +1591,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1609,7 +1613,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1624,7 +1628,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru/Gurugram Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1634,7 +1638,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1671,7 +1675,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1681,7 +1685,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1703,12 +1707,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1716,7 +1720,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1746,7 +1754,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1771,7 +1779,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1788,17 +1796,17 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1808,7 +1816,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1818,12 +1826,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -1835,17 +1843,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1855,7 +1863,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1865,12 +1873,12 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1882,17 +1890,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1902,7 +1910,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1912,12 +1920,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1929,17 +1937,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>IOS Developer</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1947,11 +1955,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1959,12 +1963,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/IOS-Developer_SR-42000</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1976,17 +1980,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1994,11 +1998,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2023,17 +2023,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2041,11 +2041,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2053,12 +2049,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://fractal.ai/en-US/Careers/job/Mumbai/Gen-AI-Engineer_SR-45659-1</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2070,17 +2066,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2088,11 +2084,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2100,12 +2092,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2117,17 +2109,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2143,12 +2135,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Mumbai/Gen-AI-Engineer_SR-45659-1</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2160,12 +2152,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2186,12 +2178,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2203,12 +2195,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2221,7 +2213,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2229,12 +2225,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2246,17 +2242,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2264,7 +2260,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2289,17 +2289,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2336,17 +2336,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Full-Stack Intern - B2B</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000148960832</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2383,12 +2383,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2430,17 +2430,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Intern - B2B</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000148960832</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2477,17 +2477,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2495,11 +2495,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>New Delhi, in</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2507,12 +2503,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2524,17 +2520,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2542,11 +2538,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2554,12 +2546,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2571,17 +2563,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities opens in a new tab</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2589,7 +2581,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2597,12 +2593,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2614,12 +2610,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2640,12 +2636,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2657,12 +2653,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2677,7 +2673,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2687,12 +2683,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2704,12 +2700,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2722,7 +2718,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7922676</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -2794,17 +2794,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2812,11 +2812,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2824,12 +2820,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7922676</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2841,17 +2837,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2859,11 +2855,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2871,12 +2863,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2888,17 +2880,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Intern - TA Tech</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2906,7 +2898,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -2914,12 +2910,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2931,27 +2927,27 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cloud Engineer </t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2961,12 +2957,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2978,27 +2974,27 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software Engineer - Fullstack </t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3008,12 +3004,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8203483?gh_jid=8203483</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3025,12 +3021,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3043,7 +3039,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3051,12 +3051,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://jobs.lever.co/paytm/f8649b65-be80-43fc-8abb-4f4d3ceb2984</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/f8649b65-be80-43fc-8abb-4f4d3ceb2984</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>Talent Acquisition Intern - Gurgaon</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Visual Design Intern- Paytm</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://jobs.lever.co/paytm/4f0b8508-1fae-45ae-bc09-67291ea3c447</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3350,17 +3350,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3368,11 +3368,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3380,12 +3376,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3397,17 +3393,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Gurgaon</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3417,7 +3413,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3427,12 +3423,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3444,12 +3440,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3462,7 +3458,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3534,17 +3534,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3552,11 +3552,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3564,12 +3560,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3581,17 +3577,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3601,7 +3597,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3611,12 +3607,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3628,12 +3624,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3646,7 +3642,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -3765,17 +3765,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3812,17 +3812,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3830,11 +3830,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3842,12 +3838,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3859,17 +3855,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Creative Producer - AI</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3877,11 +3873,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3889,12 +3881,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3906,17 +3898,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3924,7 +3916,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3932,12 +3928,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3949,17 +3945,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Creative Producer - AI</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3967,7 +3963,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -3975,12 +3975,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3992,17 +3992,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4010,11 +4010,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -4022,12 +4018,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4039,17 +4035,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4059,7 +4055,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4069,12 +4065,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4086,17 +4082,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4104,7 +4100,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4129,17 +4129,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4176,17 +4176,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Zeta</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Product Management - Intern</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bangalore - EC</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://jobs.lever.co/zeta/72ee1884-8e8b-447b-ab96-aa76605b5f4a</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://jobs.lever.co/zeta</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4220,55 +4220,8 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I83"/>
+  <autoFilter ref="A1:I82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4351,7 +4304,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4363,7 +4315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4411,35 +4363,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Log9 Materials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Log9 Materials</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.log9materials.com/careers</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4448,18 +4380,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4468,18 +4400,58 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vymo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://getvymo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Zluri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.zluri.com/careers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.zluri.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4488,18 +4460,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4508,18 +4480,38 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capillary Technologies</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.capillarytech.com/careers/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4528,18 +4520,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4548,18 +4540,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4568,46 +4560,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.firstcry.com/careers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -4631,35 +4583,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shiprocket</t>
+          <t>Coforge</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.shiprocket.in/careers/</t>
+          <t>https://www.coforge.com/careers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Coforge</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.coforge.com/careers</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4668,18 +4600,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4688,18 +4620,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
